--- a/BoM.xlsx
+++ b/BoM.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13560"/>
+    <workbookView windowWidth="28800" windowHeight="13560" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Merge" sheetId="2" r:id="rId1"/>
     <sheet name="Per Module" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Merge!$A$1:$G$54</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="203">
   <si>
     <t>Id</t>
   </si>
@@ -617,13 +618,38 @@
   </si>
   <si>
     <t>D2,D3</t>
+  </si>
+  <si>
+    <t>FR2</t>
+  </si>
+  <si>
+    <t>FR4+ML</t>
+  </si>
+  <si>
+    <t>Film</t>
+  </si>
+  <si>
+    <t>PTH</t>
+  </si>
+  <si>
+    <t>PTH+ML</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -1251,9 +1277,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1840,1050 +1875,1050 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="4">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" hidden="1" spans="1:7">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" hidden="1" spans="1:7">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="4"/>
+      <c r="G7" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="4">
         <f>1+3</f>
         <v>4</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="4"/>
+      <c r="G9" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="3" t="s">
+      <c r="F10" s="4"/>
+      <c r="G10" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="4"/>
+      <c r="G11" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="1"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="4"/>
+      <c r="G12" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="4"/>
+      <c r="G13" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="1"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="4"/>
+      <c r="G14" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="1"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="4">
         <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="4"/>
+      <c r="G15" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="4"/>
+      <c r="B16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="4">
         <v>2</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="4">
         <v>3</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="4"/>
+      <c r="B18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="4">
         <v>2</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="4"/>
+      <c r="B20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="4"/>
+      <c r="B21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="4">
         <f>2+2</f>
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="4"/>
+      <c r="G21" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="4"/>
+      <c r="B22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="4"/>
+      <c r="G22" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="4"/>
+      <c r="B23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="4">
         <v>2</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="6" t="s">
+      <c r="F23" s="4"/>
+      <c r="G23" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="4"/>
+      <c r="B24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="1"/>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="4"/>
+      <c r="B25" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="1"/>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="4"/>
+      <c r="B26" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="4">
         <v>2</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="1"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="4"/>
+      <c r="B27" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="4">
         <v>2</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="4"/>
+      <c r="B28" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="4">
         <v>2</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="1"/>
-      <c r="B29" s="3" t="s">
+      <c r="A29" s="4"/>
+      <c r="B29" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="1"/>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="4"/>
+      <c r="B30" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="1"/>
-      <c r="B31" s="3" t="s">
+      <c r="A31" s="4"/>
+      <c r="B31" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="1"/>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="4"/>
+      <c r="B32" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="1"/>
-      <c r="B33" s="3" t="s">
+      <c r="A33" s="4"/>
+      <c r="B33" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="4">
         <v>3</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="1"/>
-      <c r="B34" s="3" t="s">
+      <c r="A34" s="4"/>
+      <c r="B34" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="1"/>
-      <c r="B35" s="3" t="s">
+      <c r="A35" s="4"/>
+      <c r="B35" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="1"/>
-      <c r="B36" s="3" t="s">
+      <c r="A36" s="4"/>
+      <c r="B36" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="6" t="s">
+      <c r="F36" s="4"/>
+      <c r="G36" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="1"/>
-      <c r="B37" s="3" t="s">
+      <c r="A37" s="4"/>
+      <c r="B37" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="4">
         <v>3</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="1"/>
-      <c r="B38" s="3" t="s">
+      <c r="A38" s="4"/>
+      <c r="B38" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="6" t="s">
+      <c r="F38" s="4"/>
+      <c r="G38" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="1"/>
-      <c r="B39" s="3" t="s">
+      <c r="A39" s="4"/>
+      <c r="B39" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="4">
         <v>3</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="1"/>
-      <c r="B40" s="3" t="s">
+      <c r="A40" s="4"/>
+      <c r="B40" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="1"/>
-      <c r="B41" s="3" t="s">
+      <c r="A41" s="4"/>
+      <c r="B41" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="6" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="1"/>
-      <c r="B42" s="3" t="s">
+      <c r="A42" s="4"/>
+      <c r="B42" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="6" t="s">
+      <c r="F42" s="4"/>
+      <c r="G42" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="1"/>
-      <c r="B43" s="3" t="s">
+      <c r="A43" s="4"/>
+      <c r="B43" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="6" t="s">
+      <c r="F43" s="4"/>
+      <c r="G43" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="1"/>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="4"/>
+      <c r="B44" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="4">
         <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="6" t="s">
+      <c r="F44" s="4"/>
+      <c r="G44" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="1"/>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="4"/>
+      <c r="B45" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="6" t="s">
+      <c r="F45" s="4"/>
+      <c r="G45" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="1"/>
-      <c r="B46" s="3" t="s">
+      <c r="A46" s="4"/>
+      <c r="B46" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3" t="s">
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="6" t="s">
+      <c r="F46" s="4"/>
+      <c r="G46" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="1"/>
-      <c r="B47" s="3" t="s">
+      <c r="A47" s="4"/>
+      <c r="B47" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="4">
         <v>2</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="6" t="s">
+      <c r="F47" s="4"/>
+      <c r="G47" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="1"/>
-      <c r="B48" s="3" t="s">
+      <c r="A48" s="4"/>
+      <c r="B48" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D48" s="1">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="6" t="s">
+      <c r="F48" s="4"/>
+      <c r="G48" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="1"/>
-      <c r="B49" s="3" t="s">
+      <c r="A49" s="4"/>
+      <c r="B49" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="4">
         <f>1+1+1</f>
         <v>3</v>
       </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="6" t="s">
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="1"/>
-      <c r="B50" s="3" t="s">
+      <c r="A50" s="4"/>
+      <c r="B50" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="3" t="s">
+      <c r="D50" s="4">
+        <v>1</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5" t="s">
+      <c r="A51" s="7"/>
+      <c r="B51" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="5" t="s">
+      <c r="D51" s="7">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5" t="s">
+      <c r="A52" s="7"/>
+      <c r="B52" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="4">
-        <v>1</v>
-      </c>
-      <c r="E52" s="5" t="s">
+      <c r="D52" s="7">
+        <v>1</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="1"/>
-      <c r="B53" s="3" t="s">
+      <c r="A53" s="4"/>
+      <c r="B53" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="4">
         <f>1+2</f>
         <v>3</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="6" t="s">
+      <c r="F53" s="4"/>
+      <c r="G53" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="1"/>
-      <c r="B54" s="3" t="s">
+      <c r="A54" s="4"/>
+      <c r="B54" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="6" t="s">
+      <c r="F54" s="4"/>
+      <c r="G54" s="9" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2933,1356 +2968,1356 @@
   <dimension ref="A1:G73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="7.546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.03125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="92.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.3125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="176.8125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="7.546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="20.1875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="32.5625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.03125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="92.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="24.3125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="176.8125" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="4">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="4">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:7">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="4">
         <v>3</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="4">
         <v>3</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="4">
         <v>2</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="13" spans="2:7">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="6" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="4">
         <v>3</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:7">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="7">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="4">
         <v>2</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="D22" s="7">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="D23" s="7">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="4">
         <v>2</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="4">
         <v>2</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1" t="s">
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="7"/>
+      <c r="F32" s="10"/>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="4">
         <v>2</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3" t="s">
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3" t="s">
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="3" t="s">
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="44" spans="2:7">
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="4">
         <v>2</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="45" spans="2:7">
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="46" spans="2:7">
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="4">
         <v>2</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="47" spans="2:7">
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D47" s="1">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3" t="s">
+      <c r="D47" s="4">
+        <v>1</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="9" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="1">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="D49" s="4">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="50" spans="2:7">
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1" t="s">
+      <c r="D50" s="4">
+        <v>1</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="52" spans="2:7">
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="1">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="53" spans="2:7">
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D53" s="1">
-        <v>1</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="D53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="54" spans="2:7">
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D54" s="1">
-        <v>1</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="D54" s="4">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="55" spans="2:7">
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="1">
-        <v>1</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="D55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="56" spans="2:7">
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="1">
-        <v>1</v>
-      </c>
-      <c r="E56" s="3" t="s">
+      <c r="D56" s="4">
+        <v>1</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="57" spans="2:7">
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G57" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="58" spans="2:7">
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D58" s="1">
-        <v>1</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="59" spans="2:7">
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="1">
-        <v>1</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="D59" s="4">
+        <v>1</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="G59" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="60" spans="2:7">
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="1">
-        <v>1</v>
-      </c>
-      <c r="E60" s="3" t="s">
+      <c r="D60" s="4">
+        <v>1</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="61" spans="2:7">
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D61" s="1">
-        <v>1</v>
-      </c>
-      <c r="E61" s="3" t="s">
+      <c r="D61" s="4">
+        <v>1</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G61" s="6" t="s">
+      <c r="G61" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="62" spans="2:7">
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D62" s="1">
-        <v>1</v>
-      </c>
-      <c r="E62" s="3" t="s">
+      <c r="D62" s="4">
+        <v>1</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="2:7">
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" s="4">
         <v>3</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G63" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="2:7">
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D64" s="1">
-        <v>1</v>
-      </c>
-      <c r="E64" s="3" t="s">
+      <c r="D64" s="4">
+        <v>1</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="65" spans="2:7">
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="4">
         <v>2</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G65" s="6" t="s">
+      <c r="G65" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="66" spans="2:7">
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D66" s="1">
-        <v>1</v>
-      </c>
-      <c r="E66" s="3" t="s">
+      <c r="D66" s="4">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G66" s="6" t="s">
+      <c r="G66" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="67" spans="2:7">
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D67" s="1">
-        <v>1</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="G67" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="68" spans="2:7">
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="4">
         <v>2</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G68" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="69" spans="2:7">
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D69" s="1">
-        <v>1</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="D69" s="4">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="G69" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="70" spans="2:7">
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D70" s="1">
-        <v>1</v>
-      </c>
-      <c r="E70" s="3" t="s">
+      <c r="D70" s="4">
+        <v>1</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G70" s="6" t="s">
+      <c r="G70" s="9" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="71" spans="2:5">
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="1">
-        <v>1</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="D71" s="4">
+        <v>1</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="72" spans="2:5">
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D72" s="1">
-        <v>1</v>
-      </c>
-      <c r="E72" s="3" t="s">
+      <c r="D72" s="4">
+        <v>1</v>
+      </c>
+      <c r="E72" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="73" spans="2:7">
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="D73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G73" s="6" t="s">
+      <c r="G73" s="9" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4296,4 +4331,619 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:X22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1">
+        <v>5</v>
+      </c>
+      <c r="B1">
+        <v>9.6</v>
+      </c>
+      <c r="C1">
+        <f>A1*B1</f>
+        <v>48</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>9.7</v>
+      </c>
+      <c r="C2">
+        <f>A2*B2</f>
+        <v>48.5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K2" s="2">
+        <v>400</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="2">
+        <v>800</v>
+      </c>
+      <c r="R2" s="2">
+        <v>3</v>
+      </c>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="2">
+        <v>900</v>
+      </c>
+      <c r="V2" s="2">
+        <v>5</v>
+      </c>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>11.7</v>
+      </c>
+      <c r="C3">
+        <f>A3*B3</f>
+        <v>46.8</v>
+      </c>
+      <c r="E3" s="2">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <f>E3*F3</f>
+        <v>80</v>
+      </c>
+      <c r="H3" s="2">
+        <f>IF(G3*50&lt;20000,20000,E3*50)</f>
+        <v>20000</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2">
+        <f>G3*K2+25000+H3</f>
+        <v>77000</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2">
+        <v>12</v>
+      </c>
+      <c r="N3" s="2">
+        <v>20</v>
+      </c>
+      <c r="O3" s="2">
+        <f>M3*N3</f>
+        <v>240</v>
+      </c>
+      <c r="P3" s="2">
+        <f>IF(O3*50&lt;20000,20000,M3*50)</f>
+        <v>20000</v>
+      </c>
+      <c r="Q3" s="2">
+        <f>O3*Q2</f>
+        <v>192000</v>
+      </c>
+      <c r="R3" s="2">
+        <f>P3*R2</f>
+        <v>60000</v>
+      </c>
+      <c r="S3" s="2">
+        <f>O3*Q2+P3</f>
+        <v>212000</v>
+      </c>
+      <c r="T3" s="2">
+        <f>Q3+R3</f>
+        <v>252000</v>
+      </c>
+      <c r="U3" s="2">
+        <f>O3*U2</f>
+        <v>216000</v>
+      </c>
+      <c r="V3" s="2">
+        <f>P3*V2</f>
+        <v>100000</v>
+      </c>
+      <c r="W3" s="2">
+        <f>O3*U2+P3</f>
+        <v>236000</v>
+      </c>
+      <c r="X3" s="2">
+        <f>U3+V3</f>
+        <v>316000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>15.8</v>
+      </c>
+      <c r="C4">
+        <f>A4*B4</f>
+        <v>47.4</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+    </row>
+    <row r="5" spans="5:24">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="5:24">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="5:24">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="5:24">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="5:24">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="5:24">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="5:24">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="5:24">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="5:24">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="5:24">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="5:24">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="5:24">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="5:24">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="5:24">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="5:24">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="5:24">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="5:24">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="5:24">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:X1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/BoM.xlsx
+++ b/BoM.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Merge!$A$1:$G$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Per Module'!$A$1:$G$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Per Module'!$A$1:$G$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1277,7 +1277,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1296,16 +1296,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1368,7 +1359,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1899,450 +1890,450 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4"/>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" hidden="1" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" hidden="1" spans="1:7">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4"/>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4"/>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4"/>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="4"/>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4"/>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="4">
         <f>1+3</f>
         <v>4</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4"/>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4"/>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="4"/>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="4"/>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4"/>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="4"/>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4"/>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4"/>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="4">
         <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="4"/>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4"/>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D16" s="4">
         <v>2</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4"/>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="4">
         <v>3</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4"/>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4"/>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="4">
         <v>2</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4"/>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4"/>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D21" s="4">
         <f>2+2</f>
         <v>4</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F21" s="4"/>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4"/>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D22" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F22" s="4"/>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4"/>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D23" s="4">
         <v>2</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>63</v>
       </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4"/>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="4" t="s">
         <v>67</v>
       </c>
       <c r="F24" s="4"/>
@@ -2350,10 +2341,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4"/>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D25" s="4">
@@ -2365,10 +2356,10 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4"/>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>69</v>
       </c>
       <c r="D26" s="4">
@@ -2380,80 +2371,80 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4"/>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D27" s="4">
         <v>2</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="4" t="s">
         <v>71</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4"/>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D28" s="4">
         <v>2</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="4" t="s">
         <v>75</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4"/>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>77</v>
       </c>
       <c r="D29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="4" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="4"/>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F30" s="4"/>
@@ -2461,17 +2452,17 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4"/>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D31" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F31" s="4"/>
@@ -2479,37 +2470,37 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4"/>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="4" t="s">
         <v>85</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4"/>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D33" s="4">
         <v>3</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="4" t="s">
         <v>88</v>
       </c>
       <c r="F33" s="4"/>
@@ -2517,16 +2508,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4"/>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="4" t="s">
         <v>88</v>
       </c>
       <c r="F34" s="4"/>
@@ -2534,16 +2525,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="4"/>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="4" t="s">
         <v>88</v>
       </c>
       <c r="F35" s="4"/>
@@ -2551,267 +2542,267 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4"/>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="4" t="s">
         <v>89</v>
       </c>
       <c r="D36" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="4" t="s">
         <v>90</v>
       </c>
       <c r="F36" s="4"/>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4"/>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D37" s="4">
         <v>3</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="4" t="s">
         <v>94</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4"/>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D38" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="4" t="s">
         <v>97</v>
       </c>
       <c r="F38" s="4"/>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4"/>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="4">
         <v>3</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="4" t="s">
         <v>101</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4"/>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="4" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4"/>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>106</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="4" t="s">
         <v>107</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="4"/>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D42" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F42" s="4"/>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="4"/>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="4" t="s">
         <v>111</v>
       </c>
       <c r="D43" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F43" s="4"/>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="4"/>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="4" t="s">
         <v>113</v>
       </c>
       <c r="D44" s="4">
         <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F44" s="4"/>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="4"/>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>115</v>
       </c>
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F45" s="4"/>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="4"/>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="4" t="s">
         <v>117</v>
       </c>
       <c r="D46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F46" s="4"/>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="4"/>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>119</v>
       </c>
       <c r="D47" s="4">
         <v>2</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="4" t="s">
         <v>120</v>
       </c>
       <c r="F47" s="4"/>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="4"/>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>123</v>
       </c>
       <c r="D48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F48" s="4"/>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="4"/>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2823,102 +2814,102 @@
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="4"/>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="4" t="s">
         <v>131</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="4" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="7"/>
-      <c r="B51" s="8" t="s">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="7">
-        <v>1</v>
-      </c>
-      <c r="E51" s="8" t="s">
+      <c r="D51" s="6">
+        <v>1</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="7"/>
-      <c r="B52" s="8" t="s">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="7">
-        <v>1</v>
-      </c>
-      <c r="E52" s="8" t="s">
+      <c r="D52" s="6">
+        <v>1</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="4"/>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>137</v>
       </c>
       <c r="D53" s="4">
         <f>1+2</f>
         <v>3</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F53" s="4"/>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="4"/>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D54" s="4">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="4" t="s">
         <v>141</v>
       </c>
       <c r="F54" s="4"/>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="7" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2939,14 +2930,14 @@
             <fill>
               <patternFill patternType="solid">
                 <fgColor rgb="FFFFC7CE"/>
-                <bgColor rgb="FFFFFFFF"/>
+                <bgColor rgb="FFFFC7CE"/>
               </patternFill>
             </fill>
           </dxf>
         </dxfs>
       </extLst>
     </filterColumn>
-    <sortState ref="A2:G54">
+    <sortState ref="A1:G54">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
@@ -3002,451 +2993,451 @@
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D2" s="4">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="4">
         <v>3</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:7">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D5" s="4">
         <v>3</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="4">
         <v>3</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D10" s="4">
         <v>2</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>101</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="4" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="13" spans="2:7">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>106</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>107</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="4">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4">
         <v>3</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:7">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="7">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8" t="s">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="7">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D20" s="4">
         <v>2</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>85</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>131</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="4" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8" t="s">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="7">
-        <v>1</v>
-      </c>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8" t="s">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D23" s="7">
-        <v>1</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>137</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="4">
@@ -3454,7 +3445,7 @@
       </c>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>69</v>
       </c>
       <c r="D27" s="4">
@@ -3462,67 +3453,67 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D28" s="4">
         <v>2</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="4" t="s">
         <v>71</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D29" s="4">
         <v>2</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="4" t="s">
         <v>75</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>77</v>
       </c>
       <c r="D30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>77</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -3535,7 +3526,7 @@
       <c r="F31" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="7" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3543,338 +3534,338 @@
       <c r="A32" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="10"/>
+      <c r="F32" s="7"/>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D33" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="4" t="s">
         <v>111</v>
       </c>
       <c r="D34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>113</v>
       </c>
       <c r="D35" s="4">
         <v>2</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="4" t="s">
         <v>89</v>
       </c>
       <c r="D42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="4" t="s">
         <v>90</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="44" spans="2:7">
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="4">
         <v>2</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="4" t="s">
         <v>63</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="45" spans="2:7">
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="4" t="s">
         <v>97</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="46" spans="2:7">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="4" t="s">
         <v>137</v>
       </c>
       <c r="D46" s="4">
         <v>2</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="47" spans="2:7">
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="4" t="s">
         <v>141</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>79</v>
       </c>
       <c r="D48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="50" spans="2:7">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -3887,7 +3878,7 @@
       <c r="F50" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="7" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3897,415 +3888,415 @@
       </c>
     </row>
     <row r="52" spans="2:7">
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="53" spans="2:7">
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>111</v>
       </c>
       <c r="D53" s="4">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="54" spans="2:7">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="4" t="s">
         <v>113</v>
       </c>
       <c r="D54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="55" spans="2:7">
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>115</v>
       </c>
       <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="56" spans="2:7">
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="4" t="s">
         <v>117</v>
       </c>
       <c r="D56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="57" spans="2:7">
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="4" t="s">
         <v>119</v>
       </c>
       <c r="D57" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="4" t="s">
         <v>120</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="58" spans="2:7">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="4" t="s">
         <v>123</v>
       </c>
       <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="59" spans="2:7">
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="60" spans="2:7">
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G60" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="61" spans="2:7">
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="62" spans="2:7">
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="2:7">
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D63" s="4">
         <v>3</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G63" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="2:7">
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G64" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="65" spans="2:7">
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D65" s="4">
         <v>2</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="G65" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="66" spans="2:7">
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="4" t="s">
         <v>89</v>
       </c>
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="4" t="s">
         <v>90</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="67" spans="2:7">
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G67" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="68" spans="2:7">
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D68" s="4">
         <v>2</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" s="4" t="s">
         <v>63</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G68" s="9" t="s">
+      <c r="G68" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="69" spans="2:7">
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="4" t="s">
         <v>97</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G69" s="9" t="s">
+      <c r="G69" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="70" spans="2:7">
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="4" t="s">
         <v>141</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="G70" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="71" spans="2:5">
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="4" t="s">
         <v>79</v>
       </c>
       <c r="D71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E71" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="72" spans="2:5">
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="s">
+      <c r="E72" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="73" spans="2:7">
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C73" s="4" t="s">
@@ -4317,12 +4308,12 @@
       <c r="F73" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="G73" s="7" t="s">
         <v>128</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G72" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G73" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -4338,6 +4329,10 @@
   <sheetPr/>
   <dimension ref="A1:X22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="2" width="10.5"/>
+    <col min="4" max="5" width="10.5"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1">
@@ -4542,7 +4537,17 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
     </row>
-    <row r="5" spans="5:24">
+    <row r="5" spans="1:24">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>15.3</v>
+      </c>
+      <c r="C5">
+        <f>A5*B5</f>
+        <v>45.9</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -4630,7 +4635,11 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="5:24">
+    <row r="9" spans="2:24">
+      <c r="B9">
+        <f>0.8*18</f>
+        <v>14.4</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -4696,8 +4705,21 @@
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
     </row>
-    <row r="12" spans="5:24">
-      <c r="E12" s="2"/>
+    <row r="12" spans="2:24">
+      <c r="B12">
+        <v>400000</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ref="D12:D14" si="0">POWER(2,C12)</f>
+        <v>256</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ref="E12:E14" si="1">D12*2*B12</f>
+        <v>204800000</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -4718,8 +4740,21 @@
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
     </row>
-    <row r="13" spans="5:24">
-      <c r="E13" s="2"/>
+    <row r="13" spans="2:24">
+      <c r="B13">
+        <v>400000</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>102400000</v>
+      </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -4740,8 +4775,21 @@
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
     </row>
-    <row r="14" spans="5:24">
-      <c r="E14" s="2"/>
+    <row r="14" spans="2:24">
+      <c r="B14">
+        <v>400000</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>51200000</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -4784,10 +4832,26 @@
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
     </row>
-    <row r="16" spans="5:24">
-      <c r="E16" s="2"/>
+    <row r="16" spans="2:24">
+      <c r="B16">
+        <v>80000000</v>
+      </c>
+      <c r="C16">
+        <v>400000</v>
+      </c>
+      <c r="D16">
+        <f>B16/C16</f>
+        <v>200</v>
+      </c>
+      <c r="E16" s="2">
+        <f>LOG(D16,2)</f>
+        <v>7.64385618977473</v>
+      </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="G16" s="2">
+        <f>190*200/200</f>
+        <v>190</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
